--- a/reports/actionability_table_ko.xlsx
+++ b/reports/actionability_table_ko.xlsx
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>고정</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>즉시 바꿀 수 있어 '쉬운 경로'가 됨. 그러나 자동이체 설정이 실제 위험을 낮추지는 않아 악용 우려가 있음. 경로 포함 여부는 팀 결정. 업데이트: 아직 미결정으로 현재는 조치 가능(ACTIONABLE). 3단계: 6단계 이산 분포, 잠재 상관 -0.35, 신용 연결 가중치 0.5.</t>
+          <t>즉시 바꿀 수 있어 '쉬운 경로'가 됨. 그러나 자동이체 설정이 실제 위험을 낮추지는 않아 악용 우려가 있음. 경로 포함 여부는 팀 결정. 3단계: 6단계 이산 분포, 잠재 상관 -0.35, 신용 연결 가중치 0.5. 결정(점검 후): 자동이체 설정은 실제 위험을 낮추지 않으므로 경로에서 제외(dice_vary: false). 모델 변수로는 유지. 점검에서 거절자 4,318명에게 가장 쉬운 단일 경로(약 2.5개월)였음.</t>
         </is>
       </c>
     </row>

--- a/reports/actionability_table_ko.xlsx
+++ b/reports/actionability_table_ko.xlsx
@@ -1633,73 +1633,73 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>autopay_ratio</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>정기 청구서 자동이체 등록 비율</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>시뮬레이션</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>ACTIONABLE</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>조치 가능</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>NOT_RECOMMENDED</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>권장 불가</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>증가</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>[0.0, 1.0]</t>
         </is>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>-1 (값이 높을수록 PD 낮음)</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>고정</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>승인 경로에 포함</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>즉시 바꿀 수 있어 '쉬운 경로'가 됨. 그러나 자동이체 설정이 실제 위험을 낮추지는 않아 악용 우려가 있음. 경로 포함 여부는 팀 결정. 3단계: 6단계 이산 분포, 잠재 상관 -0.35, 신용 연결 가중치 0.5. 결정(점검 후): 자동이체 설정은 실제 위험을 낮추지 않으므로 경로에서 제외(dice_vary: false). 모델 변수로는 유지. 점검에서 거절자 4,318명에게 가장 쉬운 단일 경로(약 2.5개월)였음.</t>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>DiCE에서 고정</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>즉시 바꿀 수 있어 '쉬운 경로'가 됨. 그러나 자동이체 설정이 실제 위험을 낮추지는 않아 악용 우려가 있음. 경로 포함 여부는 팀 결정. 3단계: 6단계 이산 분포, 잠재 상관 -0.35, 신용 연결 가중치 0.5. 결정(점검 후): 자동이체 설정은 실제 위험을 낮추지 않으므로 경로에서 제외(dice_vary: false). 모델 변수로는 유지. 점검에서 거절자 4,318명에게 가장 쉬운 단일 경로(약 2.5개월)였음. 이후 분류를 권장 불가(NOT_RECOMMENDED)로 변경. 단조 제약 -1은 유지하여 최종 모델은 그대로. SHAP 거절 사유에서는 '참고(변경 불가)'로 표시.</t>
         </is>
       </c>
     </row>

--- a/reports/actionability_table_ko.xlsx
+++ b/reports/actionability_table_ko.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -499,8 +499,9 @@
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="90" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="90" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,10 +586,15 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
+          <t>모델 변수</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
           <t>경로 처리</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -656,10 +662,15 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
           <t>승인 경로에 포함</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>카드·신용한도 잔액을 갚으면 낮출 수 있음. 단계당 기간은 0.05 감소 기준. 업데이트(1단계): 원래 1 초과 값을 1로 자를 계획이었으나, 한도 초과 사용은 현실적이므로 1 초과는 유지하고 10 초과만 오류로 보아 결측 처리(util_outlier 플래그). 이에 맞춰 허용 범위를 [0, 10]으로 확대. 2단계: 10분위별 부도율 약 1.4%에서 23.4%로 증가.</t>
         </is>
@@ -733,10 +744,15 @@
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
           <t>DiCE에서 고정, 거절 사유에서 '참고(변경 불가)'로 표기</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>보호 속성. 바꿀 수 없으므로 단조 제약 불필요(제약은 AUC만 낮춤). 업데이트: 단조 제약 없이 모델 변수로 사용하기로 결정. 연령 0인 1행은 1단계에서 삭제. 공정성 참고: 연령은 리볼빙 사용률(-0.28), 부양가족 수(-0.23)와 관련되고 대체 변수와도 약하게 관련(0.05~0.09)되므로, 연령을 빼도 연령 효과가 완전히 사라지지 않음.</t>
         </is>
@@ -810,10 +826,15 @@
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
           <t>DiCE에서 고정</t>
         </is>
       </c>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>헌장 규칙 적용: 연체 이력은 감소 불가. 2년 기간 때문에 시간이 지나면 줄 수 있으나 v1에서는 고정. 업데이트(1단계): 96/98 코드(269행, 세 열 동시)는 결측 처리하고 pastdue_special_code로 표시(부도율 54.65%).</t>
         </is>
@@ -881,10 +902,15 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
           <t>포함하되 높은 비용 부여</t>
         </is>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>부채 상환이나 소득 증가가 필요. 소득 결측 행은 비정상적으로 큰 값. 업데이트: 1단계에서 소득이 결측이거나 0이면 결측 처리(비율이 아닌 금액이므로). 2단계에서 U자형으로 방향 근거가 가장 약해 제약 제거 1순위로 지정. 5단계에서 제약 비용이 AUC 0.0001에 불과해 +1 제약 유지.</t>
         </is>
@@ -954,10 +980,15 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
           <t>포함하되 높은 비용 부여</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>변경 가능하지만 외부 요인(고용)에 좌우됨. 통화 문제를 피하려고 단위를 비율(5%)로 정의. 업데이트(1단계): 결측(19.8%)은 결측으로 두고 income_missing으로 표시, 0은 실제 값으로 두고 income_zero로 표시. 대체(중앙값)는 학습 폴드에서만 계산.</t>
         </is>
@@ -1031,10 +1062,15 @@
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
           <t>DiCE에서 고정</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="P10" s="8" t="inlineStr">
         <is>
           <t>부도와 U자형 관계라 방향 제약 없음. 카드를 해지하면 사용률이 오르고, 새 계좌 개설 권유는 부적절. v1 경로에서 제외. 업데이트: 2단계에서 U자형 확인(3개 이하에서 부도율 최고). 씬파일러 규칙(2개 이하, 부동산 담보대출 0)에도 사용.</t>
         </is>
@@ -1108,10 +1144,15 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
           <t>DiCE에서 고정</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>기간 제한 없는 누적 이력. 감소 불가. 업데이트: 96/98 코드는 30~59일 열과 같이 처리. 실제 변수 중 가장 강한 예측 변수(Pearson r 0.315).</t>
         </is>
@@ -1185,10 +1226,15 @@
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
           <t>DiCE에서 고정</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>주택담보대출을 승인 경로로 제안하는 것은 비현실적. 비단조 관계. 업데이트: 2단계에서 U자형 확인. 씬파일러 규칙에도 사용.</t>
         </is>
@@ -1262,10 +1308,15 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
           <t>DiCE에서 고정</t>
         </is>
       </c>
-      <c r="O13" s="6" t="inlineStr">
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>30~59일 연체와 같은 규칙.</t>
         </is>
@@ -1339,10 +1390,15 @@
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
           <t>DiCE에서 고정, 거절 사유에서 '참고(변경 불가)'로 표기</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>가족 수를 바꾸라고 권하는 것은 비윤리적이므로 불변으로 처리. 업데이트: 결측 2.6%는 학습 폴드 중앙값으로 대체.</t>
         </is>
@@ -1351,7 +1407,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>telecom_ontime_rate</t>
+          <t>telecom_payment_rate</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1410,19 +1466,24 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
           <t>승인 경로에 포함</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>정시 납부한 달마다 1/12씩 오름. 분포는 베타 제안. 목표 상관 -0.3~-0.5. 업데이트(3단계): Beta(8, 1.5) 분포, 코퓰라 잠재 상관 -0.35, 관측 Pearson -0.27. 신용 행동과 연결(가중치 1.0, b = 0.30).</t>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>정시 납부한 달마다 1/12씩 오름. 분포는 베타 제안. 목표 상관 -0.3~-0.5. 업데이트(3단계): Beta(8, 1.5) 분포, 코퓰라 잠재 상관 -0.35, 관측 Pearson -0.27. 신용 행동과 연결(가중치 1.0, b = 0.30). 업데이트(미션 준수): 미션 변수명에 맞춰 telecom_ontime_rate에서 이름 변경. 관측 Pearson r -0.32로 보정, 다른 미션 변수와 공통 요인 공유.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>utility_ontime_rate</t>
+          <t>utility_payment_rate</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1481,12 +1542,17 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
           <t>승인 경로에 포함</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>통신요금 납부율과 상관이 높을 가능성. 둘 사이 상관도 확인 필요. 목표 상관 -0.3~-0.5. 업데이트(3단계): 통신요금 납부율과 같은 설정. 둘 사이 상관 0.19(상한 0.60)로 잡음 추가 불필요.</t>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>통신요금 납부율과 상관이 높을 가능성. 둘 사이 상관도 확인 필요. 목표 상관 -0.3~-0.5. 업데이트(3단계): 통신요금 납부율과 같은 설정. 둘 사이 상관 0.19(상한 0.60)로 잡음 추가 불필요. 업데이트(미션 준수): 미션 변수명에 맞춰 utility_ontime_rate에서 이름 변경. 관측 Pearson r -0.32로 보정, 다른 미션 변수와 공통 요인 공유.</t>
         </is>
       </c>
     </row>
@@ -1552,10 +1618,15 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
           <t>포함 시 기간만 반영, 행동 권유 문구 사용 금지</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="P17" s="9" t="inlineStr">
         <is>
           <t>행동으로 앞당길 수 없고 시간이 지나야만 증가. 분포는 감마 또는 로그정규 제안. 업데이트(3단계): Gamma(2, 24) 분포, (연령 - 18) × 12개월 상한(0.69% 행에 적용). 연령과의 상관 0.065. 신용 연결 가중치 0.5.</t>
         </is>
@@ -1623,10 +1694,15 @@
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
           <t>포함 시 기간만 반영, 행동 권유 문구 사용 금지</t>
         </is>
       </c>
-      <c r="O18" s="9" t="inlineStr">
+      <c r="P18" s="9" t="inlineStr">
         <is>
           <t>가입(직장 또는 지역)이 필요하며 시간이 지나야만 증가. 국내 대안신용평가에서 쓰이는 유형의 변수. 업데이트(3단계): Binomial(24, 0.75) 분포, 잠재 상관 -0.35, 신용 연결 가중치 0.5.</t>
         </is>
@@ -1694,255 +1770,257 @@
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
           <t>DiCE에서 고정</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>즉시 바꿀 수 있어 '쉬운 경로'가 됨. 그러나 자동이체 설정이 실제 위험을 낮추지는 않아 악용 우려가 있음. 경로 포함 여부는 팀 결정. 3단계: 6단계 이산 분포, 잠재 상관 -0.35, 신용 연결 가중치 0.5. 결정(점검 후): 자동이체 설정은 실제 위험을 낮추지 않으므로 경로에서 제외(dice_vary: false). 모델 변수로는 유지. 점검에서 거절자 4,318명에게 가장 쉬운 단일 경로(약 2.5개월)였음. 이후 분류를 권장 불가(NOT_RECOMMENDED)로 변경. 단조 제약 -1은 유지하여 최종 모델은 그대로. SHAP 거절 사유에서는 '참고(변경 불가)'로 표시.</t>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>즉시 바꿀 수 있어 '쉬운 경로'가 됨. 그러나 자동이체 설정이 실제 위험을 낮추지는 않아 악용 우려가 있음. 경로 포함 여부는 팀 결정. 3단계: 6단계 이산 분포, 잠재 상관 -0.35, 신용 연결 가중치 0.5. 결정(점검 후): 자동이체 설정은 실제 위험을 낮추지 않으므로 경로에서 제외(dice_vary: false). 모델 변수로는 유지. 점검에서 거절자 4,318명에게 가장 쉬운 단일 경로(약 2.5개월)였음. 이후 분류를 권장 불가(NOT_RECOMMENDED)로 변경. 단조 제약 -1은 유지하여 최종 모델은 그대로. SHAP 거절 사유에서는 '참고(변경 불가)'로 표시. 업데이트(미션 준수): 조작 가능한 변수가 승인 결정을 좌우하지 않도록 모델 변수에서도 제외(model_feature: false). 데이터셋에는 남아 있음.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>pastdue_special_code</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>연체 횟수 특수코드(96/98) 표시</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>파생 (1단계)</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>IMMUTABLE</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>불변</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>0 (없음)</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>spending_consistency</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>소비 일관성 점수(0~100)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>ACTIONABLE</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>조치 가능</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>증가</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>[0.0, 100.0]</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>-1 (값이 높을수록 PD 낮음)</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>승인 경로에 포함</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>미션 대체 변수. 월별 소비가 일정할수록 높음. 소비 습관을 바꾸면 올릴 수 있으므로 조치 가능. 단위 변화량(5점), 난이도(2), 단계당 기간(1개월)은 팀 가정이며 멘토 검토 필요. 시뮬레이션: Beta(5, 2) × 100, 관측 Pearson r -0.32, 공통 요인 공유, 신용 연결 가중치 0.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>regular_payment_count</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>정기결제 건수(0~20)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>NOT_RECOMMENDED</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>권장 불가</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>증가</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>[0.0, 20.0]</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>-1 (값이 높을수록 PD 낮음)</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>고정</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>DiCE에서 고정, 거절 사유에서 '참고(변경 불가)'로 표기</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>1단계에서 추가. 연체 횟수 3개 열이 모두 96/98(횟수가 아닌 특수코드)인 269행 표시. 부도율 54.65%로 신호가 강함. 과거 이력에서 나오므로 불변.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>income_missing</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>월 소득 결측 표시</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>파생 (1단계)</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>IMMUTABLE</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>불변</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>0 (없음)</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>DiCE에서 고정</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>미션 대체 변수. 정기결제를 늘리는 것은 쉽게 조작할 수 있고 실제 위험을 낮추지 않으므로(자동이체와 같은 이유) 권장 불가, 경로에서 제외. 모델 변수로는 사용. 시뮬레이션: Binomial(20, 0.75), 0~20, 관측 Pearson r -0.32, 공통 요인 공유. 미션 예시와 달리 소득과 연결하지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>app_login_frequency</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>앱 로그인 빈도(0~30)</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>NOT_RECOMMENDED</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>권장 불가</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>증가</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>[0.0, 30.0]</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>-1 (값이 높을수록 PD 낮음)</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>고정</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>DiCE에서 고정, 거절 사유에서 '참고(변경 불가)'로 표기</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>1단계에서 추가. 소득 결측 29,731행(19.8%) 표시. 이 행들은 부채비율이 금액이므로 부채비율도 결측 처리. 부도율 5.6%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>income_zero</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>월 소득 0 표시</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>파생 (1단계)</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>IMMUTABLE</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>불변</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>0 (없음)</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>고정</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>DiCE에서 고정, 거절 사유에서 '참고(변경 불가)'로 표기</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>1단계에서 추가. 소득 0인 1,634행 표시(0은 실제 값으로 유지). 이 행들의 부채비율은 결측 처리. 부도율 4.0%.</t>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>DiCE에서 고정</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>미션 대체 변수. 로그인을 늘리는 것은 순수한 조작이므로 권장 불가, 경로에서 제외. 모델 변수로는 사용. 미션 예시는 연령과 연결하지만, 연령은 보호 속성이므로 의도적으로 연결하지 않음(신용 부분은 연체 횟수와 사용률만 사용). 시뮬레이션: Binomial(30, 0.75), 0~30(로그인한 날 수), 관측 Pearson r -0.32, 공통 요인 공유.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>util_outlier</t>
+          <t>pastdue_special_code</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>리볼빙 사용률 이상치(10 초과) 표시</t>
+          <t>연체 횟수 특수코드(96/98) 표시</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2002,87 +2080,343 @@
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
           <t>DiCE에서 고정, 거절 사유에서 '참고(변경 불가)'로 표기</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>1단계에서 추가. 리볼빙 사용률 10 초과 241행 표시(데이터 오류로 보고 결측 처리). 부도율 7.05%로 평균과 비슷해 시뮬레이터에서는 중립 신용 점수 부여.</t>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>1단계에서 추가. 연체 횟수 3개 열이 모두 96/98(횟수가 아닌 특수코드)인 269행 표시. 부도율 54.65%로 신호가 강함. 과거 이력에서 나오므로 불변.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>income_missing</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>월 소득 결측 표시</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>파생 (1단계)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>IMMUTABLE</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>불변</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>0 (없음)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>고정</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>DiCE에서 고정, 거절 사유에서 '참고(변경 불가)'로 표기</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>1단계에서 추가. 소득 결측 29,731행(19.8%) 표시. 이 행들은 부채비율이 금액이므로 부채비율도 결측 처리. 부도율 5.6%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>income_zero</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>월 소득 0 표시</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>파생 (1단계)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>IMMUTABLE</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>불변</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>0 (없음)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>고정</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>DiCE에서 고정, 거절 사유에서 '참고(변경 불가)'로 표기</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>1단계에서 추가. 소득 0인 1,634행 표시(0은 실제 값으로 유지). 이 행들의 부채비율은 결측 처리. 부도율 4.0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>util_outlier</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>리볼빙 사용률 이상치(10 초과) 표시</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>파생 (1단계)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>IMMUTABLE</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>불변</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>0 (없음)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>고정</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>DiCE에서 고정, 거절 사유에서 '참고(변경 불가)'로 표기</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr">
+        <is>
+          <t>1단계에서 추가. 리볼빙 사용률 10 초과 241행 표시(데이터 오류로 보고 결측 처리). 부도율 7.05%로 평균과 비슷해 시뮬레이터에서는 중립 신용 점수 부여.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>gender_female</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>성별(여성=1, 시뮬레이션)</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>시뮬레이션</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>IMMUTABLE</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>불변</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>0 (없음)</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>예</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>고정</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>DiCE에서 고정, 거절 사유에서 '참고(변경 불가)'로 표기</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>3단계에서 추가. 50:50 시뮬레이션, 부도와 독립(r = 0.0007). 공정성 분석에만 사용하며 모델 변수로는 쓰지 않음. 보호 속성.</t>
         </is>
